--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920" tabRatio="694" activeTab="2"/>
+    <workbookView windowWidth="30240" windowHeight="12920" tabRatio="694" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
     <sheet name="ElementEnum" sheetId="7" r:id="rId2"/>
     <sheet name="ItemEnum" sheetId="8" r:id="rId3"/>
+    <sheet name="BuffEnum" sheetId="9" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -113,6 +114,48 @@
   </si>
   <si>
     <t>道具卡</t>
+  </si>
+  <si>
+    <t>BuffEnum</t>
+  </si>
+  <si>
+    <t>测试0</t>
+  </si>
+  <si>
+    <t>BuffTargetTypeEnum</t>
+  </si>
+  <si>
+    <t>我方单体</t>
+  </si>
+  <si>
+    <t>我方全体</t>
+  </si>
+  <si>
+    <t>敌方单体</t>
+  </si>
+  <si>
+    <t>敌方全体</t>
+  </si>
+  <si>
+    <t>我方部分</t>
+  </si>
+  <si>
+    <t>敌人部分</t>
+  </si>
+  <si>
+    <t>敌我全体</t>
+  </si>
+  <si>
+    <t>敌我部分</t>
+  </si>
+  <si>
+    <t>BuffType</t>
+  </si>
+  <si>
+    <t>永久</t>
+  </si>
+  <si>
+    <t>倒计时</t>
   </si>
 </sst>
 </file>
@@ -1486,4 +1529,184 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="2" max="2" width="13.6875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="219.75" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" ht="17.55" spans="2:10">
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="8:8">
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="8:8">
+      <c r="H10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="8:8">
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="8:8">
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="8:8">
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="8:8">
+      <c r="H14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="8:8">
+      <c r="H15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920" tabRatio="694" activeTab="3"/>
+    <workbookView windowWidth="30240" windowHeight="12920" tabRatio="694" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -95,7 +95,19 @@
     <t>NO1</t>
   </si>
   <si>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>PokemonTypeEnum</t>
+  </si>
+  <si>
+    <t>非玩家</t>
+  </si>
+  <si>
     <t>ElementEnum</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
   <si>
     <t>水</t>
@@ -1149,7 +1161,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="35.1339285714286" customWidth="1"/>
@@ -1255,8 +1267,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="17.55" spans="8:8">
-      <c r="H5" s="4"/>
+    <row r="5" ht="17.55" spans="8:10">
+      <c r="H5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" ht="17.55" spans="8:8">
       <c r="H6" s="4"/>
@@ -1269,6 +1286,28 @@
     </row>
     <row r="9" ht="17.55" spans="8:8">
       <c r="H9" s="4"/>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="8:10">
+      <c r="H14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1282,8 +1321,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="3"/>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1371,18 +1410,26 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="17.55" spans="2:10">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>22</v>
+      <c r="H4" t="s">
+        <v>25</v>
       </c>
       <c r="J4">
         <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="8:10">
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1491,13 +1538,13 @@
     </row>
     <row r="4" ht="17.55" spans="2:10">
       <c r="B4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1505,13 +1552,13 @@
     </row>
     <row r="13" spans="2:10">
       <c r="B13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1519,7 +1566,7 @@
     </row>
     <row r="14" spans="8:8">
       <c r="H14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1628,13 +1675,13 @@
     </row>
     <row r="4" ht="17.55" spans="2:10">
       <c r="B4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1642,64 +1689,64 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="8:8">
       <c r="H9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="8:8">
       <c r="H10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="8:8">
       <c r="H11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="8:8">
       <c r="H12" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="8:8">
       <c r="H13" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="8:8">
       <c r="H14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="8:8">
       <c r="H15" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="8:8">
       <c r="H19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -1,16 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDDD135-20BB-49FE-AE37-9CE4B43BF760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920" tabRatio="694" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="694" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
     <sheet name="ElementEnum" sheetId="7" r:id="rId2"/>
-    <sheet name="ItemEnum" sheetId="8" r:id="rId3"/>
-    <sheet name="BuffEnum" sheetId="9" r:id="rId4"/>
+    <sheet name="RaceEnum" sheetId="10" r:id="rId3"/>
+    <sheet name="ItemEnum" sheetId="8" r:id="rId4"/>
+    <sheet name="BuffEnum" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -21,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -168,19 +173,21 @@
   </si>
   <si>
     <t>倒计时</t>
+  </si>
+  <si>
+    <t>机械</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RaceEnum</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,155 +199,27 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -349,198 +228,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799615466780602"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79958494827112647"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -578,255 +271,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -836,68 +287,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1155,19 +565,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="35.1339285714286" customWidth="1"/>
+    <col min="2" max="2" width="35.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1189,15 +599,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1223,7 +633,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219.75" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1253,41 +663,41 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="17.55" spans="2:10">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="17.55" spans="8:10">
-      <c r="H5" s="4" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="17.55" spans="8:8">
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" ht="17.55" spans="8:8">
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" ht="17.55" spans="8:8">
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" ht="17.55" spans="8:8">
-      <c r="H9" s="4"/>
-    </row>
-    <row r="13" spans="2:10">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>22</v>
       </c>
@@ -1301,7 +711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="8:10">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H14" t="s">
         <v>23</v>
       </c>
@@ -1313,18 +723,17 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1346,15 +755,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1380,7 +789,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219.75" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1410,7 +819,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -1424,7 +833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:10">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H5" t="s">
         <v>26</v>
       </c>
@@ -1436,21 +845,17 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
-  <cols>
-    <col min="2" max="2" width="15.7678571428571" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{414CD9CA-AB79-42B9-9926-C20D9FF4477A}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1472,15 +877,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1506,7 +911,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219.75" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1536,58 +941,46 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="17.55" spans="2:10">
-      <c r="B4" t="s">
-        <v>27</v>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>28</v>
+      <c r="H4" t="s">
+        <v>25</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="8:8">
-      <c r="H14" t="s">
-        <v>31</v>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.6875" customWidth="1"/>
+    <col min="2" max="2" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1609,15 +1002,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1643,7 +1036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219.75" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1673,87 +1066,223 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="17.55" spans="2:10">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>33</v>
+      <c r="H4" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="8:8">
-      <c r="H9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="8:8">
-      <c r="H10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="8:8">
-      <c r="H11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="8:8">
-      <c r="H12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="8:8">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
       <c r="H13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="8:8">
+        <v>30</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="8:8">
-      <c r="H15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="8:8">
-      <c r="H19" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="13.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -1,23 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDDD135-20BB-49FE-AE37-9CE4B43BF760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="694" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="30240" windowHeight="12920" tabRatio="694" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
     <sheet name="ElementEnum" sheetId="7" r:id="rId2"/>
     <sheet name="RaceEnum" sheetId="10" r:id="rId3"/>
-    <sheet name="ItemEnum" sheetId="8" r:id="rId4"/>
-    <sheet name="BuffEnum" sheetId="9" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId4"/>
+    <sheet name="ItemEnum" sheetId="8" r:id="rId5"/>
+    <sheet name="BuffEnum" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,6 +23,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -118,6 +115,15 @@
     <t>水</t>
   </si>
   <si>
+    <t>RaceEnum</t>
+  </si>
+  <si>
+    <t>机械</t>
+  </si>
+  <si>
+    <t>PassiveEnum</t>
+  </si>
+  <si>
     <t>ItemEnum</t>
   </si>
   <si>
@@ -133,6 +139,9 @@
     <t>道具卡</t>
   </si>
   <si>
+    <t>不知道</t>
+  </si>
+  <si>
     <t>BuffEnum</t>
   </si>
   <si>
@@ -173,21 +182,19 @@
   </si>
   <si>
     <t>倒计时</t>
-  </si>
-  <si>
-    <t>机械</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RaceEnum</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,14 +206,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -214,12 +213,155 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -228,12 +370,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79958494827112647"/>
+        <fgColor theme="9" tint="0.799584948271126"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -271,9 +599,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -287,27 +857,71 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -565,19 +1179,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="35.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -599,15 +1213,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,7 +1247,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+    <row r="3" ht="219.75" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -663,41 +1277,41 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" ht="17.55" spans="2:10">
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H5" s="3" t="s">
+    <row r="5" ht="17.55" spans="8:10">
+      <c r="H5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H9" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" ht="17.55" spans="8:8">
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" ht="17.55" spans="8:8">
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" ht="17.55" spans="8:8">
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" ht="17.55" spans="8:8">
+      <c r="H9" s="4"/>
+    </row>
+    <row r="13" spans="2:10">
       <c r="B13" t="s">
         <v>22</v>
       </c>
@@ -711,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="8:10">
       <c r="H14" t="s">
         <v>23</v>
       </c>
@@ -723,17 +1337,18 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -755,15 +1370,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +1404,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -819,7 +1434,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -833,7 +1448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="8:10">
       <c r="H5" t="s">
         <v>26</v>
       </c>
@@ -845,17 +1460,18 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{414CD9CA-AB79-42B9-9926-C20D9FF4477A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -877,15 +1493,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -911,7 +1527,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -941,9 +1557,9 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B4" s="4" t="s">
-        <v>47</v>
+    <row r="4" spans="2:10">
+      <c r="B4" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -955,9 +1571,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H5" s="4" t="s">
-        <v>46</v>
+    <row r="5" spans="8:10">
+      <c r="H5" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -967,20 +1583,21 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="15.75" customWidth="1"/>
+    <col min="2" max="2" width="15.1696428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1002,15 +1619,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1036,7 +1653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1066,57 +1683,42 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>27</v>
+    <row r="4" spans="2:10">
+      <c r="B4" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>28</v>
+      <c r="H4" t="s">
+        <v>25</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H14" t="s">
-        <v>31</v>
-      </c>
+    <row r="5" spans="8:8">
+      <c r="H5" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="13.75" customWidth="1"/>
+    <col min="2" max="2" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1138,15 +1740,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1172,7 +1774,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+    <row r="3" ht="219.75" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1202,87 +1804,229 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>33</v>
+      <c r="H4" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+    <row r="13" spans="2:10">
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="8:8">
+      <c r="H14" t="s">
         <v>34</v>
       </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
+    </row>
+    <row r="15" spans="8:8">
+      <c r="H15" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H19" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="2" max="2" width="13.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="219.75" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" ht="17.55" spans="2:10">
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="8:8">
+      <c r="H9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="8:8">
+      <c r="H10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="8:8">
+      <c r="H11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="8:8">
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="8:8">
+      <c r="H13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="8:8">
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="8:8">
+      <c r="H15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920" tabRatio="694" activeTab="4"/>
+    <workbookView windowWidth="28000" windowHeight="12920" tabRatio="694" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -124,22 +124,28 @@
     <t>PassiveEnum</t>
   </si>
   <si>
+    <t>ItemTypeEnum</t>
+  </si>
+  <si>
+    <t>卡牌</t>
+  </si>
+  <si>
+    <t>不知道</t>
+  </si>
+  <si>
+    <t>CardTypeEnum</t>
+  </si>
+  <si>
+    <t>地形卡</t>
+  </si>
+  <si>
+    <t>道具卡</t>
+  </si>
+  <si>
     <t>ItemEnum</t>
   </si>
   <si>
     <t>回血0</t>
-  </si>
-  <si>
-    <t>ItemTypeEnum</t>
-  </si>
-  <si>
-    <t>地形卡</t>
-  </si>
-  <si>
-    <t>道具卡</t>
-  </si>
-  <si>
-    <t>不知道</t>
   </si>
   <si>
     <t>BuffEnum</t>
@@ -194,7 +200,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,13 +210,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -717,133 +716,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -863,7 +862,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1712,7 +1711,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="15.75" customWidth="1"/>
@@ -1774,7 +1773,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219.75" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1811,35 +1810,46 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" t="s">
         <v>31</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="5" spans="8:8">
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="8:8">
+      <c r="H9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="17.55" spans="2:10">
       <c r="B13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="H13" t="s">
-        <v>33</v>
+      <c r="H13" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="J13">
         <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="8:8">
-      <c r="H14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="8:8">
-      <c r="H15" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1948,13 +1958,13 @@
     </row>
     <row r="4" ht="17.55" spans="2:10">
       <c r="B4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1962,64 +1972,64 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="8:8">
       <c r="H9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="8:8">
       <c r="H10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="8:8">
       <c r="H11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="8:8">
       <c r="H12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="8:8">
       <c r="H13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="8:8">
       <c r="H14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="8:8">
       <c r="H15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="8:8">
       <c r="H19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="12920" tabRatio="694" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="10620" tabRatio="694" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
     <sheet name="ElementEnum" sheetId="7" r:id="rId2"/>
     <sheet name="RaceEnum" sheetId="10" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId4"/>
+    <sheet name="PassiveEnum" sheetId="11" r:id="rId4"/>
     <sheet name="ItemEnum" sheetId="8" r:id="rId5"/>
     <sheet name="BuffEnum" sheetId="9" r:id="rId6"/>
   </sheets>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="72">
   <si>
     <t>##var</t>
   </si>
@@ -97,13 +97,13 @@
     <t>NO1</t>
   </si>
   <si>
-    <t>玩家</t>
+    <t>Player</t>
   </si>
   <si>
     <t>PokemonTypeEnum</t>
   </si>
   <si>
-    <t>非玩家</t>
+    <t>NonePlayer</t>
   </si>
   <si>
     <t>ElementEnum</t>
@@ -118,12 +118,45 @@
     <t>RaceEnum</t>
   </si>
   <si>
-    <t>机械</t>
+    <t>Ghost</t>
+  </si>
+  <si>
+    <t>Spirit</t>
+  </si>
+  <si>
+    <t>Animal</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>Robot</t>
+  </si>
+  <si>
+    <t>Insect</t>
   </si>
   <si>
     <t>PassiveEnum</t>
   </si>
   <si>
+    <t>Evolution</t>
+  </si>
+  <si>
+    <t>Collecting</t>
+  </si>
+  <si>
+    <t>SpreadSeed</t>
+  </si>
+  <si>
+    <t>HugeWeapon</t>
+  </si>
+  <si>
+    <t>Loyalty</t>
+  </si>
+  <si>
+    <t>SuperSpeed</t>
+  </si>
+  <si>
     <t>ItemTypeEnum</t>
   </si>
   <si>
@@ -136,16 +169,43 @@
     <t>CardTypeEnum</t>
   </si>
   <si>
-    <t>地形卡</t>
-  </si>
-  <si>
-    <t>道具卡</t>
+    <t>Terrain</t>
+  </si>
+  <si>
+    <t>Stuff</t>
   </si>
   <si>
     <t>ItemEnum</t>
   </si>
   <si>
-    <t>回血0</t>
+    <t>BigForest</t>
+  </si>
+  <si>
+    <t>MineMountain</t>
+  </si>
+  <si>
+    <t>Grave</t>
+  </si>
+  <si>
+    <t>BattleTower</t>
+  </si>
+  <si>
+    <t>MetalFactory</t>
+  </si>
+  <si>
+    <t>SpeedUpgrade</t>
+  </si>
+  <si>
+    <t>ArmorUpgrade</t>
+  </si>
+  <si>
+    <t>RebirthUpgrade</t>
+  </si>
+  <si>
+    <t>EnergyDrink</t>
+  </si>
+  <si>
+    <t>DirtyMop</t>
   </si>
   <si>
     <t>BuffEnum</t>
@@ -200,7 +260,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +271,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -360,7 +427,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,6 +442,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -560,7 +633,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -593,6 +666,34 @@
       <top style="medium">
         <color rgb="FFDEE0E3"/>
       </top>
+      <bottom style="medium">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FFDEE0E3"/>
       </bottom>
@@ -716,55 +817,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -779,90 +877,102 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1185,9 +1295,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="35.125" customWidth="1"/>
+    <col min="2" max="2" width="35.1296296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1212,13 +1322,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1246,14 +1356,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219.75" spans="1:12">
+    <row r="3" ht="180.15" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1276,7 +1386,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="17.55" spans="2:10">
+    <row r="4" ht="14.55" spans="2:10">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1290,7 +1400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="17.55" spans="8:10">
+    <row r="5" spans="8:10">
       <c r="H5" s="4" t="s">
         <v>21</v>
       </c>
@@ -1298,16 +1408,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="17.55" spans="8:8">
+    <row r="6" ht="14.55" spans="8:8">
       <c r="H6" s="4"/>
     </row>
-    <row r="7" ht="17.55" spans="8:8">
+    <row r="7" ht="14.55" spans="8:8">
       <c r="H7" s="4"/>
     </row>
-    <row r="8" ht="17.55" spans="8:8">
+    <row r="8" ht="14.55" spans="8:8">
       <c r="H8" s="4"/>
     </row>
-    <row r="9" ht="17.55" spans="8:8">
+    <row r="9" ht="14.55" spans="8:8">
       <c r="H9" s="4"/>
     </row>
     <row r="13" spans="2:10">
@@ -1345,7 +1455,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9.12962962962963" defaultRowHeight="13.8" outlineLevelRow="4"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1369,13 +1479,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1403,14 +1513,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="179.4" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1467,8 +1577,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1492,13 +1602,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1526,14 +1636,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="179.4" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1557,7 +1667,7 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="b">
@@ -1571,11 +1681,51 @@
       </c>
     </row>
     <row r="5" spans="8:10">
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="J5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="8:10">
+      <c r="H6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="8:10">
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="8:10">
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="8:10">
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="8:10">
+      <c r="H10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1590,10 +1740,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="15.1696428571429" customWidth="1"/>
+    <col min="2" max="2" width="15.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1618,13 +1768,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1652,14 +1802,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="179.4" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1683,8 +1833,8 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="5" t="s">
-        <v>29</v>
+      <c r="B4" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -1696,8 +1846,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
-      <c r="H5" s="5"/>
+    <row r="5" ht="14.55" spans="8:10">
+      <c r="H5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="14.55" spans="8:10">
+      <c r="H6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="14.55" spans="8:10">
+      <c r="H7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" ht="14.55" spans="8:10">
+      <c r="H8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="14.55" spans="8:10">
+      <c r="H9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" ht="14.55" spans="8:10">
+      <c r="H10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1711,8 +1906,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr defaultColWidth="9.12962962962963" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="15.75" customWidth="1"/>
   </cols>
@@ -1739,13 +1934,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1773,14 +1968,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="179.4" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1805,13 +2000,13 @@
     </row>
     <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1819,37 +2014,115 @@
     </row>
     <row r="5" spans="8:8">
       <c r="H5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
       <c r="B8" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="8:8">
+        <v>45</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="8:10">
       <c r="H9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" ht="17.55" spans="2:10">
+        <v>46</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
       <c r="B13" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>37</v>
+      <c r="H13" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="J13">
         <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="8:10">
+      <c r="H14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="8:10">
+      <c r="H15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="8:10">
+      <c r="H16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="8:10">
+      <c r="H17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="8:10">
+      <c r="H18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="8:10">
+      <c r="H19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="8:10">
+      <c r="H20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="8:10">
+      <c r="H21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="8:10">
+      <c r="H22" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J22">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1865,7 +2138,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.12962962962963" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="13.75" customWidth="1"/>
   </cols>
@@ -1892,13 +2165,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1926,14 +2199,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219.75" spans="1:12">
+    <row r="3" ht="180.15" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1956,15 +2229,15 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="17.55" spans="2:10">
+    <row r="4" ht="14.55" spans="2:10">
       <c r="B4" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1972,64 +2245,64 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="8:8">
       <c r="H9" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="8:8">
       <c r="H10" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="8:8">
       <c r="H11" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="8:8">
       <c r="H12" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="8:8">
       <c r="H13" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="8:8">
       <c r="H14" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="8:8">
       <c r="H15" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="8:8">
       <c r="H19" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10620" tabRatio="694" activeTab="3"/>
+    <workbookView windowWidth="28000" windowHeight="12920" tabRatio="694"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="71">
   <si>
     <t>##var</t>
   </si>
@@ -94,16 +94,16 @@
     <t>PokemonEnum</t>
   </si>
   <si>
-    <t>NO1</t>
-  </si>
-  <si>
-    <t>Player</t>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>测试0</t>
   </si>
   <si>
     <t>PokemonTypeEnum</t>
   </si>
   <si>
-    <t>NonePlayer</t>
+    <t>普通</t>
   </si>
   <si>
     <t>ElementEnum</t>
@@ -169,49 +169,46 @@
     <t>CardTypeEnum</t>
   </si>
   <si>
-    <t>Terrain</t>
-  </si>
-  <si>
-    <t>Stuff</t>
+    <t>地形卡</t>
+  </si>
+  <si>
+    <t>道具卡</t>
   </si>
   <si>
     <t>ItemEnum</t>
   </si>
   <si>
-    <t>BigForest</t>
-  </si>
-  <si>
-    <t>MineMountain</t>
-  </si>
-  <si>
-    <t>Grave</t>
-  </si>
-  <si>
-    <t>BattleTower</t>
-  </si>
-  <si>
-    <t>MetalFactory</t>
-  </si>
-  <si>
-    <t>SpeedUpgrade</t>
-  </si>
-  <si>
-    <t>ArmorUpgrade</t>
-  </si>
-  <si>
-    <t>RebirthUpgrade</t>
-  </si>
-  <si>
-    <t>EnergyDrink</t>
-  </si>
-  <si>
-    <t>DirtyMop</t>
+    <t>大森林</t>
+  </si>
+  <si>
+    <t>矿山</t>
+  </si>
+  <si>
+    <t>墓园</t>
+  </si>
+  <si>
+    <t>战斗哨塔</t>
+  </si>
+  <si>
+    <t>废铁厂</t>
+  </si>
+  <si>
+    <t>高速升级</t>
+  </si>
+  <si>
+    <t>装甲升级</t>
+  </si>
+  <si>
+    <t>重组升级</t>
+  </si>
+  <si>
+    <t>能量饮料</t>
+  </si>
+  <si>
+    <t>脏拖把</t>
   </si>
   <si>
     <t>BuffEnum</t>
-  </si>
-  <si>
-    <t>测试0</t>
   </si>
   <si>
     <t>BuffTargetTypeEnum</t>
@@ -427,7 +424,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -442,7 +439,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -823,7 +838,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -847,16 +862,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -865,105 +880,114 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1295,9 +1319,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="35.1296296296296" customWidth="1"/>
+    <col min="2" max="2" width="35.1339285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1322,13 +1346,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1356,14 +1380,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="180.15" spans="1:12">
+    <row r="3" ht="219.75" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1386,7 +1410,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="14.55" spans="2:10">
+    <row r="4" ht="17.55" spans="2:10">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1408,16 +1432,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="14.55" spans="8:8">
+    <row r="6" ht="17.55" spans="8:8">
       <c r="H6" s="4"/>
     </row>
-    <row r="7" ht="14.55" spans="8:8">
+    <row r="7" ht="17.55" spans="8:8">
       <c r="H7" s="4"/>
     </row>
-    <row r="8" ht="14.55" spans="8:8">
+    <row r="8" ht="17.55" spans="8:8">
       <c r="H8" s="4"/>
     </row>
-    <row r="9" ht="14.55" spans="8:8">
+    <row r="9" ht="17.55" spans="8:8">
       <c r="H9" s="4"/>
     </row>
     <row r="13" spans="2:10">
@@ -1428,7 +1452,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1455,7 +1479,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.12962962962963" defaultRowHeight="13.8" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9.13392857142857" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1479,13 +1503,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1513,14 +1537,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="179.4" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1578,7 +1602,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1602,13 +1626,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1636,14 +1660,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="179.4" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1667,7 +1691,7 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="9" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="b">
@@ -1681,7 +1705,7 @@
       </c>
     </row>
     <row r="5" spans="8:10">
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="9" t="s">
         <v>28</v>
       </c>
       <c r="J5">
@@ -1741,9 +1765,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="15.1666666666667" customWidth="1"/>
+    <col min="2" max="2" width="15.1696428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1768,13 +1792,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1802,14 +1826,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="179.4" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1833,7 +1857,7 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D4" t="b">
@@ -1846,48 +1870,48 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="14.55" spans="8:10">
-      <c r="H5" s="7" t="s">
+    <row r="5" ht="17.55" spans="8:10">
+      <c r="H5" s="10" t="s">
         <v>35</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="14.55" spans="8:10">
-      <c r="H6" s="8" t="s">
+    <row r="6" ht="17.55" spans="8:10">
+      <c r="H6" s="11" t="s">
         <v>36</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="14.55" spans="8:10">
-      <c r="H7" s="8" t="s">
+    <row r="7" ht="17.55" spans="8:10">
+      <c r="H7" s="11" t="s">
         <v>37</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="14.55" spans="8:10">
-      <c r="H8" s="8" t="s">
+    <row r="8" ht="17.55" spans="8:10">
+      <c r="H8" s="11" t="s">
         <v>38</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="14.55" spans="8:10">
-      <c r="H9" s="8" t="s">
+    <row r="9" ht="17.55" spans="8:10">
+      <c r="H9" s="11" t="s">
         <v>39</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="14.55" spans="8:10">
-      <c r="H10" s="8" t="s">
+    <row r="10" ht="17.55" spans="8:10">
+      <c r="H10" s="11" t="s">
         <v>40</v>
       </c>
       <c r="J10">
@@ -1907,7 +1931,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9.12962962962963" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9.13392857142857" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="15.75" customWidth="1"/>
   </cols>
@@ -1934,13 +1958,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1968,14 +1992,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="179.4" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2049,7 +2073,8 @@
       <c r="H13" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J13">
+      <c r="I13" s="7"/>
+      <c r="J13" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2057,7 +2082,8 @@
       <c r="H14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J14">
+      <c r="I14" s="7"/>
+      <c r="J14" s="7">
         <v>1</v>
       </c>
     </row>
@@ -2065,7 +2091,8 @@
       <c r="H15" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="J15">
+      <c r="I15" s="7"/>
+      <c r="J15" s="7">
         <v>2</v>
       </c>
     </row>
@@ -2073,7 +2100,8 @@
       <c r="H16" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J16">
+      <c r="I16" s="7"/>
+      <c r="J16" s="7">
         <v>3</v>
       </c>
     </row>
@@ -2081,47 +2109,53 @@
       <c r="H17" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J17">
+      <c r="I17" s="7"/>
+      <c r="J17" s="7">
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="8:10">
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="J18">
+      <c r="I18" s="8"/>
+      <c r="J18" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="8:10">
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J19">
+      <c r="I19" s="8"/>
+      <c r="J19" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="20" spans="8:10">
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="J20">
+      <c r="I20" s="8"/>
+      <c r="J20" s="8">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="8:10">
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="J21">
+      <c r="I21" s="8"/>
+      <c r="J21" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="8:10">
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="J22">
+      <c r="I22" s="8"/>
+      <c r="J22" s="8">
         <v>9</v>
       </c>
     </row>
@@ -2138,7 +2172,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="9.12962962962963" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9.13392857142857" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="13.75" customWidth="1"/>
   </cols>
@@ -2165,13 +2199,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2199,14 +2233,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="180.15" spans="1:12">
+    <row r="3" ht="219.75" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2229,7 +2263,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="14.55" spans="2:10">
+    <row r="4" ht="17.55" spans="2:10">
       <c r="B4" t="s">
         <v>58</v>
       </c>
@@ -2237,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2245,64 +2279,64 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="8:8">
       <c r="H9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="8:8">
       <c r="H10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="8:8">
       <c r="H11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="8:8">
       <c r="H12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="8:8">
       <c r="H13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="8:8">
       <c r="H14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="8:8">
       <c r="H15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="8:8">
       <c r="H19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="12920" tabRatio="694"/>
+    <workbookView windowWidth="28000" windowHeight="12920" tabRatio="694" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -161,9 +161,6 @@
   </si>
   <si>
     <t>卡牌</t>
-  </si>
-  <si>
-    <t>不知道</t>
   </si>
   <si>
     <t>CardTypeEnum</t>
@@ -424,7 +421,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,13 +436,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -838,7 +829,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -862,16 +853,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -880,89 +871,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -978,16 +969,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1424,7 +1418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:10">
+    <row r="5" ht="17.55" spans="8:10">
       <c r="H5" s="4" t="s">
         <v>21</v>
       </c>
@@ -1691,7 +1685,7 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="b">
@@ -1705,7 +1699,7 @@
       </c>
     </row>
     <row r="5" spans="8:10">
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>28</v>
       </c>
       <c r="J5">
@@ -1857,7 +1851,7 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D4" t="b">
@@ -1871,7 +1865,7 @@
       </c>
     </row>
     <row r="5" ht="17.55" spans="8:10">
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J5">
@@ -1879,7 +1873,7 @@
       </c>
     </row>
     <row r="6" ht="17.55" spans="8:10">
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>36</v>
       </c>
       <c r="J6">
@@ -1887,7 +1881,7 @@
       </c>
     </row>
     <row r="7" ht="17.55" spans="8:10">
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="12" t="s">
         <v>37</v>
       </c>
       <c r="J7">
@@ -1895,7 +1889,7 @@
       </c>
     </row>
     <row r="8" ht="17.55" spans="8:10">
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="J8">
@@ -1903,7 +1897,7 @@
       </c>
     </row>
     <row r="9" ht="17.55" spans="8:10">
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="12" t="s">
         <v>39</v>
       </c>
       <c r="J9">
@@ -1911,7 +1905,7 @@
       </c>
     </row>
     <row r="10" ht="17.55" spans="8:10">
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="12" t="s">
         <v>40</v>
       </c>
       <c r="J10">
@@ -1930,7 +1924,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9.13392857142857" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="15.75" customWidth="1"/>
@@ -2030,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2038,18 +2032,18 @@
     </row>
     <row r="5" spans="8:8">
       <c r="H5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="2:10">
       <c r="B8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2057,7 +2051,7 @@
     </row>
     <row r="9" spans="8:10">
       <c r="H9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -2065,99 +2059,86 @@
     </row>
     <row r="13" spans="2:10">
       <c r="B13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="8:10">
+      <c r="H14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="8:10">
+      <c r="H15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="8:10">
-      <c r="H14" s="5" t="s">
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="8:10">
+      <c r="H16" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="8:10">
-      <c r="H15" s="5" t="s">
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="8:10">
+      <c r="H17" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="8:10">
-      <c r="H16" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="8:10">
-      <c r="H17" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7">
-        <v>4</v>
-      </c>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="8:10">
       <c r="H18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="8:10">
+      <c r="H19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="8:10">
+      <c r="H20" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="8:10">
-      <c r="H19" s="6" t="s">
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="8:10">
+      <c r="H21" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="8:10">
-      <c r="H20" s="6" t="s">
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="8:10">
+      <c r="H22" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="8:10">
-      <c r="H21" s="6" t="s">
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="8:10">
+      <c r="H23" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="8:10">
-      <c r="H22" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8">
-        <v>9</v>
-      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2265,7 +2246,7 @@
     </row>
     <row r="4" ht="17.55" spans="2:10">
       <c r="B4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -2279,64 +2260,64 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="8:8">
       <c r="H9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="8:8">
       <c r="H10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="8:8">
       <c r="H11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="8:8">
       <c r="H12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="8:8">
       <c r="H13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="8:8">
       <c r="H14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="8:8">
       <c r="H15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="8:8">
       <c r="H19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="12920" tabRatio="694" activeTab="4"/>
+    <workbookView windowWidth="25600" windowHeight="12080" tabRatio="694"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="104">
   <si>
     <t>##var</t>
   </si>
@@ -97,115 +97,217 @@
     <t>玩家</t>
   </si>
   <si>
+    <t>灯笼鬼</t>
+  </si>
+  <si>
+    <t>小幽魂</t>
+  </si>
+  <si>
+    <t>笨笨甲熊</t>
+  </si>
+  <si>
+    <t>枯木妖</t>
+  </si>
+  <si>
+    <t>烈火领主</t>
+  </si>
+  <si>
+    <t>落叶蝴蝶</t>
+  </si>
+  <si>
+    <t>一口鲸</t>
+  </si>
+  <si>
+    <t>铁刀客</t>
+  </si>
+  <si>
+    <t>围巾狸</t>
+  </si>
+  <si>
+    <t>研究体0号</t>
+  </si>
+  <si>
+    <t>猛毒蝎</t>
+  </si>
+  <si>
+    <t>负树龟</t>
+  </si>
+  <si>
+    <t>PokemonTypeEnum</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>ElementEnum</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>RaceEnum</t>
+  </si>
+  <si>
+    <t>Ghost</t>
+  </si>
+  <si>
+    <t>Spirit</t>
+  </si>
+  <si>
+    <t>Animal</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>Robot</t>
+  </si>
+  <si>
+    <t>Insect</t>
+  </si>
+  <si>
+    <t>PassiveEnum</t>
+  </si>
+  <si>
+    <t>Evolution</t>
+  </si>
+  <si>
+    <t>Collecting</t>
+  </si>
+  <si>
+    <t>SpreadSeed</t>
+  </si>
+  <si>
+    <t>HugeWeapon</t>
+  </si>
+  <si>
+    <t>Loyalty</t>
+  </si>
+  <si>
+    <t>SuperSpeed</t>
+  </si>
+  <si>
+    <t>捡拾</t>
+  </si>
+  <si>
+    <t>水晶诅咒</t>
+  </si>
+  <si>
+    <t>常规机械</t>
+  </si>
+  <si>
+    <t>枯木逢春</t>
+  </si>
+  <si>
+    <t>高温</t>
+  </si>
+  <si>
+    <t>下毒</t>
+  </si>
+  <si>
+    <t>大口吃</t>
+  </si>
+  <si>
+    <t>一刀斩</t>
+  </si>
+  <si>
+    <t>屯屯</t>
+  </si>
+  <si>
+    <t>仇恨滔天</t>
+  </si>
+  <si>
+    <t>猛毒</t>
+  </si>
+  <si>
+    <t>负重前行</t>
+  </si>
+  <si>
+    <t>ItemTypeEnum</t>
+  </si>
+  <si>
+    <t>卡牌</t>
+  </si>
+  <si>
+    <t>CardTypeEnum</t>
+  </si>
+  <si>
+    <t>地形卡</t>
+  </si>
+  <si>
+    <t>道具卡</t>
+  </si>
+  <si>
+    <t>ItemEnum</t>
+  </si>
+  <si>
+    <t>大森林</t>
+  </si>
+  <si>
+    <t>矿山</t>
+  </si>
+  <si>
+    <t>墓园</t>
+  </si>
+  <si>
+    <t>战斗哨塔</t>
+  </si>
+  <si>
+    <t>废铁厂</t>
+  </si>
+  <si>
+    <t>高速升级</t>
+  </si>
+  <si>
+    <t>装甲升级</t>
+  </si>
+  <si>
+    <t>重组升级</t>
+  </si>
+  <si>
+    <t>能量饮料</t>
+  </si>
+  <si>
+    <t>脏拖把</t>
+  </si>
+  <si>
+    <t>BuffEnum</t>
+  </si>
+  <si>
     <t>测试0</t>
   </si>
   <si>
-    <t>PokemonTypeEnum</t>
-  </si>
-  <si>
-    <t>普通</t>
-  </si>
-  <si>
-    <t>ElementEnum</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>水</t>
-  </si>
-  <si>
-    <t>RaceEnum</t>
-  </si>
-  <si>
-    <t>Ghost</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>Animal</t>
-  </si>
-  <si>
-    <t>Plant</t>
-  </si>
-  <si>
-    <t>Robot</t>
-  </si>
-  <si>
-    <t>Insect</t>
-  </si>
-  <si>
-    <t>PassiveEnum</t>
-  </si>
-  <si>
-    <t>Evolution</t>
-  </si>
-  <si>
-    <t>Collecting</t>
-  </si>
-  <si>
-    <t>SpreadSeed</t>
-  </si>
-  <si>
-    <t>HugeWeapon</t>
-  </si>
-  <si>
-    <t>Loyalty</t>
-  </si>
-  <si>
-    <t>SuperSpeed</t>
-  </si>
-  <si>
-    <t>ItemTypeEnum</t>
-  </si>
-  <si>
-    <t>卡牌</t>
-  </si>
-  <si>
-    <t>CardTypeEnum</t>
-  </si>
-  <si>
-    <t>地形卡</t>
-  </si>
-  <si>
-    <t>道具卡</t>
-  </si>
-  <si>
-    <t>ItemEnum</t>
-  </si>
-  <si>
-    <t>大森林</t>
-  </si>
-  <si>
-    <t>矿山</t>
-  </si>
-  <si>
-    <t>墓园</t>
-  </si>
-  <si>
-    <t>战斗哨塔</t>
-  </si>
-  <si>
-    <t>废铁厂</t>
-  </si>
-  <si>
-    <t>高速升级</t>
-  </si>
-  <si>
-    <t>装甲升级</t>
-  </si>
-  <si>
-    <t>重组升级</t>
-  </si>
-  <si>
-    <t>能量饮料</t>
-  </si>
-  <si>
-    <t>脏拖把</t>
-  </si>
-  <si>
-    <t>BuffEnum</t>
+    <t>易损</t>
+  </si>
+  <si>
+    <t>暴虐</t>
+  </si>
+  <si>
+    <t>吸血</t>
+  </si>
+  <si>
+    <t>肉质</t>
+  </si>
+  <si>
+    <t>寄生</t>
+  </si>
+  <si>
+    <t>灼伤</t>
+  </si>
+  <si>
+    <t>储藏</t>
+  </si>
+  <si>
+    <t>升级</t>
+  </si>
+  <si>
+    <t>神经毒素</t>
+  </si>
+  <si>
+    <t>高额伤害</t>
   </si>
   <si>
     <t>BuffTargetTypeEnum</t>
@@ -421,7 +523,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,6 +551,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -829,7 +937,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -853,16 +961,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -871,104 +979,110 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -992,6 +1106,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1312,10 +1432,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="35.1339285714286" customWidth="1"/>
+    <col min="2" max="2" width="35.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1340,13 +1460,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1374,14 +1494,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219.75" spans="1:12">
+    <row r="3" ht="168.75" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1404,7 +1524,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="17.55" spans="2:10">
+    <row r="4" ht="14.75" spans="2:10">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1418,45 +1538,121 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="17.55" spans="8:10">
-      <c r="H5" s="4" t="s">
+    <row r="5" spans="8:10">
+      <c r="H5" s="16" t="s">
         <v>21</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="17.55" spans="8:8">
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" ht="17.55" spans="8:8">
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" ht="17.55" spans="8:8">
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" ht="17.55" spans="8:8">
-      <c r="H9" s="4"/>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" t="s">
+    <row r="6" spans="8:10">
+      <c r="H6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D13" t="b">
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="8:10">
+      <c r="H7" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="8:10">
+      <c r="H8" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="8:10">
+      <c r="H9" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="8:10">
+      <c r="H10" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="8:10">
+      <c r="H11" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="8:10">
+      <c r="H12" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="8:10">
+      <c r="H13" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="8:10">
+      <c r="H14" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="8:10">
+      <c r="H15" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="8:10">
+      <c r="H16" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="b">
         <v>1</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H25" t="s">
         <v>20</v>
       </c>
-      <c r="J13">
+      <c r="J25">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="8:10">
-      <c r="H14" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14">
+    <row r="26" spans="8:10">
+      <c r="H26" t="s">
+        <v>34</v>
+      </c>
+      <c r="J26">
         <v>1</v>
       </c>
     </row>
@@ -1473,7 +1669,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.13392857142857" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9.13333333333333" defaultRowHeight="14" outlineLevelRow="4"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1497,13 +1693,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1531,14 +1727,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1563,13 +1759,13 @@
     </row>
     <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1577,7 +1773,7 @@
     </row>
     <row r="5" spans="8:10">
       <c r="H5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1596,7 +1792,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1620,13 +1816,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1654,14 +1850,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1685,22 +1881,22 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="10" t="s">
-        <v>27</v>
+      <c r="B4" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="8:10">
-      <c r="H5" s="10" t="s">
-        <v>28</v>
+      <c r="H5" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1708,7 +1904,7 @@
     </row>
     <row r="6" spans="8:10">
       <c r="H6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -1716,7 +1912,7 @@
     </row>
     <row r="7" spans="8:10">
       <c r="H7" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="J7">
         <v>3</v>
@@ -1724,7 +1920,7 @@
     </row>
     <row r="8" spans="8:10">
       <c r="H8" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -1732,7 +1928,7 @@
     </row>
     <row r="9" spans="8:10">
       <c r="H9" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1740,7 +1936,7 @@
     </row>
     <row r="10" spans="8:10">
       <c r="H10" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1758,10 +1954,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="15.1696428571429" customWidth="1"/>
+    <col min="2" max="2" width="15.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1786,13 +1982,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1820,14 +2016,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1851,65 +2047,161 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="10" t="s">
-        <v>34</v>
+      <c r="B4" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="17.55" spans="8:10">
-      <c r="H5" s="11" t="s">
-        <v>35</v>
+    <row r="5" ht="14.75" spans="8:10">
+      <c r="H5" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="17.55" spans="8:10">
-      <c r="H6" s="12" t="s">
-        <v>36</v>
+    <row r="6" ht="14.75" spans="8:10">
+      <c r="H6" s="14" t="s">
+        <v>47</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="17.55" spans="8:10">
-      <c r="H7" s="12" t="s">
-        <v>37</v>
+    <row r="7" ht="14.75" spans="8:10">
+      <c r="H7" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="17.55" spans="8:10">
-      <c r="H8" s="12" t="s">
-        <v>38</v>
+    <row r="8" ht="14.75" spans="8:10">
+      <c r="H8" s="14" t="s">
+        <v>49</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="17.55" spans="8:10">
-      <c r="H9" s="12" t="s">
-        <v>39</v>
+    <row r="9" ht="14.75" spans="8:10">
+      <c r="H9" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="17.55" spans="8:10">
-      <c r="H10" s="12" t="s">
-        <v>40</v>
+    <row r="10" ht="14.75" spans="8:10">
+      <c r="H10" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="J10">
         <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="8:10">
+      <c r="H11" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="8:10">
+      <c r="H12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="8:10">
+      <c r="H13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="8:10">
+      <c r="H14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="8:10">
+      <c r="H15" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="8:10">
+      <c r="H16" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="J16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="8:10">
+      <c r="H17" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="8:10">
+      <c r="H18" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="8:10">
+      <c r="H19" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="8:10">
+      <c r="H20" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="8:10">
+      <c r="H21" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="8:10">
+      <c r="H22" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="J22">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1925,7 +2217,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9.13392857142857" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.13333333333333" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15.75" customWidth="1"/>
   </cols>
@@ -1952,13 +2244,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1986,14 +2278,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2018,13 +2310,13 @@
     </row>
     <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2032,18 +2324,18 @@
     </row>
     <row r="5" spans="8:8">
       <c r="H5" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="2:10">
       <c r="B8" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2051,7 +2343,7 @@
     </row>
     <row r="9" spans="8:10">
       <c r="H9" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -2059,86 +2351,86 @@
     </row>
     <row r="13" spans="2:10">
       <c r="B13" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="H13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" spans="8:10">
-      <c r="H14" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
+      <c r="H14" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
     </row>
     <row r="15" spans="8:10">
-      <c r="H15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
+      <c r="H15" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
     </row>
     <row r="16" spans="8:10">
-      <c r="H16" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
+      <c r="H16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
     </row>
     <row r="17" spans="8:10">
-      <c r="H17" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
+      <c r="H17" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
     </row>
     <row r="18" spans="8:10">
-      <c r="H18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
+      <c r="H18" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
     </row>
     <row r="19" spans="8:10">
-      <c r="H19" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="H19" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
     </row>
     <row r="20" spans="8:10">
-      <c r="H20" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="H20" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
     </row>
     <row r="21" spans="8:10">
-      <c r="H21" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="H21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
     </row>
     <row r="22" spans="8:10">
-      <c r="H22" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
+      <c r="H22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
     </row>
     <row r="23" spans="8:10">
-      <c r="H23" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
+      <c r="H23" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2152,8 +2444,8 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="9.13392857142857" defaultRowHeight="16.8"/>
+  <dimension ref="A1:L29"/>
+  <sheetFormatPr defaultColWidth="9.13333333333333" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.75" customWidth="1"/>
   </cols>
@@ -2180,13 +2472,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2214,14 +2506,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219.75" spans="1:12">
+    <row r="3" ht="168.75" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2244,80 +2536,160 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="17.55" spans="2:10">
+    <row r="4" ht="14.75" spans="2:10">
       <c r="B4" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" t="b">
+    <row r="5" spans="8:10">
+      <c r="H5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J5">
         <v>1</v>
       </c>
-      <c r="H8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="8:8">
-      <c r="H9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="8:8">
-      <c r="H10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="8:8">
-      <c r="H11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="8:8">
-      <c r="H12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="8:8">
-      <c r="H13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="8:8">
-      <c r="H14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="8:8">
-      <c r="H15" t="s">
-        <v>66</v>
+    </row>
+    <row r="6" spans="8:10">
+      <c r="H6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="8:10">
+      <c r="H7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="8:10">
+      <c r="H8" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="8:10">
+      <c r="H9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="8:10">
+      <c r="H10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="8:10">
+      <c r="H11" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="8:10">
+      <c r="H12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="8:10">
+      <c r="H13" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="8:10">
+      <c r="H14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J14">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="8:8">
       <c r="H19" t="s">
-        <v>69</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="8:8">
+      <c r="H21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="8:8">
+      <c r="H22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="8:8">
+      <c r="H23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="8:8">
+      <c r="H24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="8:8">
+      <c r="H25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="8:8">
+      <c r="H29" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31AFB8D9-07A4-45B2-B3DF-C62C42B0C708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" tabRatio="694"/>
+    <workbookView xWindow="10215" yWindow="1545" windowWidth="15540" windowHeight="12930" tabRatio="694" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
@@ -23,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -232,131 +236,127 @@
     <t>卡牌</t>
   </si>
   <si>
+    <t>道具卡</t>
+  </si>
+  <si>
+    <t>ItemEnum</t>
+  </si>
+  <si>
+    <t>大森林</t>
+  </si>
+  <si>
+    <t>矿山</t>
+  </si>
+  <si>
+    <t>墓园</t>
+  </si>
+  <si>
+    <t>战斗哨塔</t>
+  </si>
+  <si>
+    <t>废铁厂</t>
+  </si>
+  <si>
+    <t>高速升级</t>
+  </si>
+  <si>
+    <t>装甲升级</t>
+  </si>
+  <si>
+    <t>重组升级</t>
+  </si>
+  <si>
+    <t>能量饮料</t>
+  </si>
+  <si>
+    <t>脏拖把</t>
+  </si>
+  <si>
+    <t>BuffEnum</t>
+  </si>
+  <si>
+    <t>测试0</t>
+  </si>
+  <si>
+    <t>易损</t>
+  </si>
+  <si>
+    <t>暴虐</t>
+  </si>
+  <si>
+    <t>吸血</t>
+  </si>
+  <si>
+    <t>肉质</t>
+  </si>
+  <si>
+    <t>寄生</t>
+  </si>
+  <si>
+    <t>灼伤</t>
+  </si>
+  <si>
+    <t>储藏</t>
+  </si>
+  <si>
+    <t>升级</t>
+  </si>
+  <si>
+    <t>神经毒素</t>
+  </si>
+  <si>
+    <t>高额伤害</t>
+  </si>
+  <si>
+    <t>BuffTargetTypeEnum</t>
+  </si>
+  <si>
+    <t>我方单体</t>
+  </si>
+  <si>
+    <t>我方全体</t>
+  </si>
+  <si>
+    <t>敌方单体</t>
+  </si>
+  <si>
+    <t>敌方全体</t>
+  </si>
+  <si>
+    <t>我方部分</t>
+  </si>
+  <si>
+    <t>敌人部分</t>
+  </si>
+  <si>
+    <t>敌我全体</t>
+  </si>
+  <si>
+    <t>敌我部分</t>
+  </si>
+  <si>
+    <t>BuffType</t>
+  </si>
+  <si>
+    <t>永久</t>
+  </si>
+  <si>
+    <t>倒计时</t>
+  </si>
+  <si>
+    <t>地形卡</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>CardTypeEnum</t>
-  </si>
-  <si>
-    <t>地形卡</t>
-  </si>
-  <si>
-    <t>道具卡</t>
-  </si>
-  <si>
-    <t>ItemEnum</t>
-  </si>
-  <si>
-    <t>大森林</t>
-  </si>
-  <si>
-    <t>矿山</t>
-  </si>
-  <si>
-    <t>墓园</t>
-  </si>
-  <si>
-    <t>战斗哨塔</t>
-  </si>
-  <si>
-    <t>废铁厂</t>
-  </si>
-  <si>
-    <t>高速升级</t>
-  </si>
-  <si>
-    <t>装甲升级</t>
-  </si>
-  <si>
-    <t>重组升级</t>
-  </si>
-  <si>
-    <t>能量饮料</t>
-  </si>
-  <si>
-    <t>脏拖把</t>
-  </si>
-  <si>
-    <t>BuffEnum</t>
-  </si>
-  <si>
-    <t>测试0</t>
-  </si>
-  <si>
-    <t>易损</t>
-  </si>
-  <si>
-    <t>暴虐</t>
-  </si>
-  <si>
-    <t>吸血</t>
-  </si>
-  <si>
-    <t>肉质</t>
-  </si>
-  <si>
-    <t>寄生</t>
-  </si>
-  <si>
-    <t>灼伤</t>
-  </si>
-  <si>
-    <t>储藏</t>
-  </si>
-  <si>
-    <t>升级</t>
-  </si>
-  <si>
-    <t>神经毒素</t>
-  </si>
-  <si>
-    <t>高额伤害</t>
-  </si>
-  <si>
-    <t>BuffTargetTypeEnum</t>
-  </si>
-  <si>
-    <t>我方单体</t>
-  </si>
-  <si>
-    <t>我方全体</t>
-  </si>
-  <si>
-    <t>敌方单体</t>
-  </si>
-  <si>
-    <t>敌方全体</t>
-  </si>
-  <si>
-    <t>我方部分</t>
-  </si>
-  <si>
-    <t>敌人部分</t>
-  </si>
-  <si>
-    <t>敌我全体</t>
-  </si>
-  <si>
-    <t>敌我部分</t>
-  </si>
-  <si>
-    <t>BuffType</t>
-  </si>
-  <si>
-    <t>永久</t>
-  </si>
-  <si>
-    <t>倒计时</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,6 +368,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -375,155 +376,27 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -532,7 +405,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799584948271126"/>
+        <fgColor theme="9" tint="0.79955442976165048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,13 +417,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,194 +433,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -813,263 +500,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1080,16 +522,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
@@ -1098,13 +537,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1113,62 +549,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1426,19 +824,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="35.1333333333333" customWidth="1"/>
+    <col min="2" max="2" width="35.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1460,15 +858,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1494,14 +892,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168.75" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1524,117 +922,117 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="14.75" spans="2:10">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:10">
-      <c r="H5" s="16" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="13" t="s">
         <v>21</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="8:10">
-      <c r="H6" s="16" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H6" s="13" t="s">
         <v>22</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="8:10">
-      <c r="H7" s="16" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" s="13" t="s">
         <v>23</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="8:10">
-      <c r="H8" s="16" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" s="13" t="s">
         <v>24</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="8:10">
-      <c r="H9" s="16" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" s="13" t="s">
         <v>25</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="8:10">
-      <c r="H10" s="16" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H10" s="13" t="s">
         <v>26</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="8:10">
-      <c r="H11" s="16" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" s="13" t="s">
         <v>27</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="8:10">
-      <c r="H12" s="16" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" s="13" t="s">
         <v>28</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="8:10">
-      <c r="H13" s="16" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" s="13" t="s">
         <v>29</v>
       </c>
       <c r="J13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="8:10">
-      <c r="H14" s="16" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="13" t="s">
         <v>30</v>
       </c>
       <c r="J14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="8:10">
-      <c r="H15" s="16" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" s="13" t="s">
         <v>31</v>
       </c>
       <c r="J15">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="8:10">
-      <c r="H16" s="16" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="13" t="s">
         <v>32</v>
       </c>
       <c r="J16">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>33</v>
       </c>
@@ -1648,7 +1046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="8:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H26" t="s">
         <v>34</v>
       </c>
@@ -1660,18 +1058,17 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.13333333333333" defaultRowHeight="14" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1693,15 +1090,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1727,14 +1124,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1757,7 +1154,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>35</v>
       </c>
@@ -1771,7 +1168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:10">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H5" t="s">
         <v>37</v>
       </c>
@@ -1783,18 +1180,17 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1816,15 +1212,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1850,14 +1246,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1880,8 +1276,8 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
-      <c r="B4" s="12" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
         <v>38</v>
       </c>
       <c r="D4" t="b">
@@ -1894,15 +1290,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:10">
-      <c r="H5" s="12" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
         <v>39</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="8:10">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H6" t="s">
         <v>40</v>
       </c>
@@ -1910,7 +1306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="8:10">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H7" t="s">
         <v>41</v>
       </c>
@@ -1918,7 +1314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="8:10">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H8" t="s">
         <v>42</v>
       </c>
@@ -1926,7 +1322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="8:10">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H9" t="s">
         <v>43</v>
       </c>
@@ -1934,7 +1330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="8:10">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H10" t="s">
         <v>44</v>
       </c>
@@ -1946,21 +1342,20 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.1666666666667" customWidth="1"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1982,15 +1377,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2016,14 +1411,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2046,8 +1441,8 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
-      <c r="B4" s="12" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
         <v>45</v>
       </c>
       <c r="D4" t="b">
@@ -2060,144 +1455,144 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="14.75" spans="8:10">
-      <c r="H5" s="13" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="10" t="s">
         <v>46</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="14.75" spans="8:10">
-      <c r="H6" s="14" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H6" s="11" t="s">
         <v>47</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="14.75" spans="8:10">
-      <c r="H7" s="14" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" s="11" t="s">
         <v>48</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="14.75" spans="8:10">
-      <c r="H8" s="14" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" s="11" t="s">
         <v>49</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="14.75" spans="8:10">
-      <c r="H9" s="14" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" s="11" t="s">
         <v>50</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="14.75" spans="8:10">
-      <c r="H10" s="14" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H10" s="11" t="s">
         <v>51</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="8:10">
-      <c r="H11" s="15" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" s="12" t="s">
         <v>52</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="8:10">
-      <c r="H12" s="15" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" s="12" t="s">
         <v>53</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="8:10">
-      <c r="H13" s="15" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" s="12" t="s">
         <v>54</v>
       </c>
       <c r="J13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="8:10">
-      <c r="H14" s="15" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="12" t="s">
         <v>55</v>
       </c>
       <c r="J14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="8:10">
-      <c r="H15" s="15" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J15">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="8:10">
-      <c r="H16" s="15" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="12" t="s">
         <v>57</v>
       </c>
       <c r="J16">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="8:10">
-      <c r="H17" s="15" t="s">
+    <row r="17" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H17" s="12" t="s">
         <v>58</v>
       </c>
       <c r="J17">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="8:10">
-      <c r="H18" s="15" t="s">
+    <row r="18" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H18" s="12" t="s">
         <v>59</v>
       </c>
       <c r="J18">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="8:10">
-      <c r="H19" s="15" t="s">
+    <row r="19" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H19" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J19">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="8:10">
-      <c r="H20" s="15" t="s">
+    <row r="20" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H20" s="12" t="s">
         <v>61</v>
       </c>
       <c r="J20">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="8:10">
-      <c r="H21" s="15" t="s">
+    <row r="21" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H21" s="12" t="s">
         <v>62</v>
       </c>
       <c r="J21">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="8:10">
-      <c r="H22" s="15" t="s">
+    <row r="22" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H22" s="12" t="s">
         <v>63</v>
       </c>
       <c r="J22">
@@ -2208,21 +1603,20 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9.13333333333333" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2244,15 +1638,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2278,14 +1672,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2308,7 +1702,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>64</v>
       </c>
@@ -2322,135 +1716,134 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
-      <c r="B8" t="s">
-        <v>66</v>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="15" t="s">
+        <v>103</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
-      <c r="H8" t="s">
-        <v>67</v>
+      <c r="H8" s="15" t="s">
+        <v>102</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="8:10">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" t="s">
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-    </row>
-    <row r="14" spans="8:10">
-      <c r="H14" s="8" t="s">
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-    </row>
-    <row r="15" spans="8:10">
-      <c r="H15" s="8" t="s">
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H17" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-    </row>
-    <row r="16" spans="8:10">
-      <c r="H16" s="8" t="s">
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H18" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-    </row>
-    <row r="17" spans="8:10">
-      <c r="H17" s="8" t="s">
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H19" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-    </row>
-    <row r="18" spans="8:10">
-      <c r="H18" s="8" t="s">
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H20" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-    </row>
-    <row r="19" spans="8:10">
-      <c r="H19" s="9" t="s">
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H21" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-    </row>
-    <row r="20" spans="8:10">
-      <c r="H20" s="9" t="s">
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H22" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-    </row>
-    <row r="21" spans="8:10">
-      <c r="H21" s="9" t="s">
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H23" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-    </row>
-    <row r="22" spans="8:10">
-      <c r="H22" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-    </row>
-    <row r="23" spans="8:10">
-      <c r="H23" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L29"/>
-  <sheetFormatPr defaultColWidth="9.13333333333333" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2472,15 +1865,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2506,14 +1899,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168.75" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2536,167 +1929,167 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="14.75" spans="2:10">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>81</v>
+      <c r="H4" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:10">
-      <c r="H5" s="5" t="s">
-        <v>82</v>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="8:10">
-      <c r="H6" s="5" t="s">
-        <v>83</v>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H6" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="8:10">
-      <c r="H7" s="5" t="s">
-        <v>84</v>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="8:10">
-      <c r="H8" s="5" t="s">
-        <v>85</v>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="8:10">
-      <c r="H9" s="5" t="s">
-        <v>86</v>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="8:10">
-      <c r="H10" s="5" t="s">
-        <v>87</v>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H10" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="8:10">
-      <c r="H11" s="5" t="s">
-        <v>88</v>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="8:10">
-      <c r="H12" s="5" t="s">
-        <v>89</v>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="8:10">
-      <c r="H13" s="5" t="s">
-        <v>90</v>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="J13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="8:10">
-      <c r="H14" s="6" t="s">
-        <v>91</v>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="J14">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
         <v>92</v>
       </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="8:8">
-      <c r="H19" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="8:8">
-      <c r="H20" t="s">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="8:8">
-      <c r="H21" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="8:8">
-      <c r="H22" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H24" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="8:8">
-      <c r="H23" t="s">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="24" spans="8:8">
-      <c r="H24" t="s">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="25" spans="8:8">
-      <c r="H25" t="s">
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
-      <c r="B28" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
         <v>101</v>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" spans="8:8">
-      <c r="H29" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31AFB8D9-07A4-45B2-B3DF-C62C42B0C708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10215" yWindow="1545" windowWidth="15540" windowHeight="12930" tabRatio="694" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="30240" windowHeight="12920" tabRatio="694" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
@@ -19,6 +13,7 @@
     <sheet name="PassiveEnum" sheetId="11" r:id="rId4"/>
     <sheet name="ItemEnum" sheetId="8" r:id="rId5"/>
     <sheet name="BuffEnum" sheetId="9" r:id="rId6"/>
+    <sheet name="GroupEnum" sheetId="12" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,6 +24,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="119">
   <si>
     <t>##var</t>
   </si>
@@ -167,7 +164,7 @@
     <t>Plant</t>
   </si>
   <si>
-    <t>Robot</t>
+    <t>机械</t>
   </si>
   <si>
     <t>Insect</t>
@@ -236,6 +233,12 @@
     <t>卡牌</t>
   </si>
   <si>
+    <t>CardTypeEnum</t>
+  </si>
+  <si>
+    <t>地形卡</t>
+  </si>
+  <si>
     <t>道具卡</t>
   </si>
   <si>
@@ -272,6 +275,42 @@
     <t>脏拖把</t>
   </si>
   <si>
+    <t>BuffTargetTypeEnum</t>
+  </si>
+  <si>
+    <t>我方单体</t>
+  </si>
+  <si>
+    <t>我方全体</t>
+  </si>
+  <si>
+    <t>敌方单体</t>
+  </si>
+  <si>
+    <t>敌方全体</t>
+  </si>
+  <si>
+    <t>我方部分</t>
+  </si>
+  <si>
+    <t>敌人部分</t>
+  </si>
+  <si>
+    <t>敌我全体</t>
+  </si>
+  <si>
+    <t>敌我部分</t>
+  </si>
+  <si>
+    <t>BuffType</t>
+  </si>
+  <si>
+    <t>永久</t>
+  </si>
+  <si>
+    <t>倒计时</t>
+  </si>
+  <si>
     <t>BuffEnum</t>
   </si>
   <si>
@@ -308,55 +347,62 @@
     <t>高额伤害</t>
   </si>
   <si>
-    <t>BuffTargetTypeEnum</t>
-  </si>
-  <si>
-    <t>我方单体</t>
-  </si>
-  <si>
-    <t>我方全体</t>
-  </si>
-  <si>
-    <t>敌方单体</t>
-  </si>
-  <si>
-    <t>敌方全体</t>
-  </si>
-  <si>
-    <t>我方部分</t>
-  </si>
-  <si>
-    <t>敌人部分</t>
-  </si>
-  <si>
-    <t>敌我全体</t>
-  </si>
-  <si>
-    <t>敌我部分</t>
-  </si>
-  <si>
-    <t>BuffType</t>
-  </si>
-  <si>
-    <t>永久</t>
-  </si>
-  <si>
-    <t>倒计时</t>
-  </si>
-  <si>
-    <t>地形卡</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CardTypeEnum</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>永久速度</t>
+  </si>
+  <si>
+    <t>永久固定防御力</t>
+  </si>
+  <si>
+    <t>永久固定力量</t>
+  </si>
+  <si>
+    <t>永久固定生命值</t>
+  </si>
+  <si>
+    <t>临时固定速度</t>
+  </si>
+  <si>
+    <t>临时固定力量</t>
+  </si>
+  <si>
+    <t>临时固定防御</t>
+  </si>
+  <si>
+    <t>恢复百分比生命</t>
+  </si>
+  <si>
+    <t>受到固定真实伤害</t>
+  </si>
+  <si>
+    <t>下次攻击伤害倍率</t>
+  </si>
+  <si>
+    <t>降低百分比力量</t>
+  </si>
+  <si>
+    <t>GroupEnum</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>友方</t>
+  </si>
+  <si>
+    <t>敌方</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,7 +414,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -376,27 +428,155 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -405,7 +585,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79955442976165048"/>
+        <fgColor theme="9" tint="0.79955442976165"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,13 +597,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,8 +613,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -454,21 +820,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFDEE0E3"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -494,15 +845,272 @@
       <right style="medium">
         <color rgb="FFDEE0E3"/>
       </right>
+      <top style="medium">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
+      </right>
       <top/>
       <bottom style="medium">
         <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -516,19 +1124,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
@@ -540,33 +1154,71 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -824,19 +1476,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="35.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -858,15 +1510,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -892,7 +1544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+    <row r="3" ht="219.75" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -922,117 +1574,117 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" ht="17.55" spans="2:10">
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="5" t="s">
         <v>20</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H5" s="13" t="s">
+    <row r="5" spans="8:10">
+      <c r="H5" s="15" t="s">
         <v>21</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H6" s="13" t="s">
+    <row r="6" spans="8:10">
+      <c r="H6" s="15" t="s">
         <v>22</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H7" s="13" t="s">
+    <row r="7" spans="8:10">
+      <c r="H7" s="15" t="s">
         <v>23</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H8" s="13" t="s">
+    <row r="8" spans="8:10">
+      <c r="H8" s="15" t="s">
         <v>24</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H9" s="13" t="s">
+    <row r="9" spans="8:10">
+      <c r="H9" s="15" t="s">
         <v>25</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H10" s="13" t="s">
+    <row r="10" spans="8:10">
+      <c r="H10" s="15" t="s">
         <v>26</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H11" s="13" t="s">
+    <row r="11" spans="8:10">
+      <c r="H11" s="15" t="s">
         <v>27</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H12" s="13" t="s">
+    <row r="12" spans="8:10">
+      <c r="H12" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H13" s="13" t="s">
+    <row r="13" spans="8:10">
+      <c r="H13" s="15" t="s">
         <v>29</v>
       </c>
       <c r="J13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H14" s="13" t="s">
+    <row r="14" spans="8:10">
+      <c r="H14" s="15" t="s">
         <v>30</v>
       </c>
       <c r="J14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H15" s="13" t="s">
+    <row r="15" spans="8:10">
+      <c r="H15" s="15" t="s">
         <v>31</v>
       </c>
       <c r="J15">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H16" s="13" t="s">
+    <row r="16" spans="8:10">
+      <c r="H16" s="15" t="s">
         <v>32</v>
       </c>
       <c r="J16">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:10">
       <c r="B25" t="s">
         <v>33</v>
       </c>
@@ -1046,7 +1698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="8:10">
       <c r="H26" t="s">
         <v>34</v>
       </c>
@@ -1058,17 +1710,18 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1090,15 +1743,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1124,7 +1777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1154,7 +1807,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>35</v>
       </c>
@@ -1168,7 +1821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="8:10">
       <c r="H5" t="s">
         <v>37</v>
       </c>
@@ -1180,17 +1833,18 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1212,15 +1866,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1246,7 +1900,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1276,7 +1930,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>38</v>
       </c>
@@ -1290,7 +1944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="8:10">
       <c r="H5" t="s">
         <v>39</v>
       </c>
@@ -1298,7 +1952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="8:10">
       <c r="H6" t="s">
         <v>40</v>
       </c>
@@ -1306,7 +1960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="8:10">
       <c r="H7" t="s">
         <v>41</v>
       </c>
@@ -1314,7 +1968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="8:10">
       <c r="H8" t="s">
         <v>42</v>
       </c>
@@ -1322,7 +1976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="8:10">
       <c r="H9" t="s">
         <v>43</v>
       </c>
@@ -1330,7 +1984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="8:10">
       <c r="H10" t="s">
         <v>44</v>
       </c>
@@ -1342,20 +1996,21 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1377,15 +2032,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1411,7 +2066,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1441,7 +2096,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>45</v>
       </c>
@@ -1455,144 +2110,144 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H5" s="10" t="s">
+    <row r="5" ht="17.55" spans="8:10">
+      <c r="H5" s="12" t="s">
         <v>46</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H6" s="11" t="s">
+    <row r="6" ht="17.55" spans="8:10">
+      <c r="H6" s="13" t="s">
         <v>47</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H7" s="11" t="s">
+    <row r="7" ht="17.55" spans="8:10">
+      <c r="H7" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H8" s="11" t="s">
+    <row r="8" ht="17.55" spans="8:10">
+      <c r="H8" s="13" t="s">
         <v>49</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H9" s="11" t="s">
+    <row r="9" ht="17.55" spans="8:10">
+      <c r="H9" s="13" t="s">
         <v>50</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H10" s="11" t="s">
+    <row r="10" ht="17.55" spans="8:10">
+      <c r="H10" s="13" t="s">
         <v>51</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H11" s="12" t="s">
+    <row r="11" spans="8:10">
+      <c r="H11" s="14" t="s">
         <v>52</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H12" s="12" t="s">
+    <row r="12" spans="8:10">
+      <c r="H12" s="14" t="s">
         <v>53</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H13" s="12" t="s">
+    <row r="13" spans="8:10">
+      <c r="H13" s="14" t="s">
         <v>54</v>
       </c>
       <c r="J13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H14" s="12" t="s">
+    <row r="14" spans="8:10">
+      <c r="H14" s="14" t="s">
         <v>55</v>
       </c>
       <c r="J14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H15" s="12" t="s">
+    <row r="15" spans="8:10">
+      <c r="H15" s="14" t="s">
         <v>56</v>
       </c>
       <c r="J15">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H16" s="12" t="s">
+    <row r="16" spans="8:10">
+      <c r="H16" s="14" t="s">
         <v>57</v>
       </c>
       <c r="J16">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H17" s="12" t="s">
+    <row r="17" spans="8:10">
+      <c r="H17" s="14" t="s">
         <v>58</v>
       </c>
       <c r="J17">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H18" s="12" t="s">
+    <row r="18" spans="8:10">
+      <c r="H18" s="14" t="s">
         <v>59</v>
       </c>
       <c r="J18">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H19" s="12" t="s">
+    <row r="19" spans="8:10">
+      <c r="H19" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J19">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H20" s="12" t="s">
+    <row r="20" spans="8:10">
+      <c r="H20" s="14" t="s">
         <v>61</v>
       </c>
       <c r="J20">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H21" s="12" t="s">
+    <row r="21" spans="8:10">
+      <c r="H21" s="14" t="s">
         <v>62</v>
       </c>
       <c r="J21">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H22" s="12" t="s">
+    <row r="22" spans="8:10">
+      <c r="H22" s="14" t="s">
         <v>63</v>
       </c>
       <c r="J22">
@@ -1603,20 +2258,21 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1638,15 +2294,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1672,7 +2328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1702,7 +2358,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>64</v>
       </c>
@@ -1716,134 +2372,135 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="8:8">
       <c r="H5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B8" s="15" t="s">
-        <v>103</v>
+    <row r="8" spans="2:10">
+      <c r="B8" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="15" t="s">
-        <v>102</v>
+      <c r="H8" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="8:10">
       <c r="H9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:10">
       <c r="B13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H14" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H15" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H16" s="6" t="s">
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" spans="8:10">
+      <c r="H14" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H17" s="6" t="s">
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" spans="8:10">
+      <c r="H15" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H18" s="6" t="s">
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" spans="8:10">
+      <c r="H16" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H19" s="7" t="s">
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+    </row>
+    <row r="17" spans="8:10">
+      <c r="H17" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-    </row>
-    <row r="20" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H20" s="7" t="s">
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+    </row>
+    <row r="18" spans="8:10">
+      <c r="H18" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-    </row>
-    <row r="21" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H21" s="7" t="s">
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" spans="8:10">
+      <c r="H19" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-    </row>
-    <row r="22" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H22" s="7" t="s">
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+    </row>
+    <row r="20" spans="8:10">
+      <c r="H20" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-    </row>
-    <row r="23" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H23" s="7" t="s">
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+    </row>
+    <row r="21" spans="8:10">
+      <c r="H21" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+    </row>
+    <row r="22" spans="8:10">
+      <c r="H22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+    </row>
+    <row r="23" spans="8:10">
+      <c r="H23" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:L29"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1865,15 +2522,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1899,7 +2556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1929,167 +2586,361 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J4">
+      <c r="H4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="8:8">
+      <c r="H5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
+      <c r="H6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="8:8">
+      <c r="H7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="8:8">
+      <c r="H8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="8:8">
+      <c r="H9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="8:8">
+      <c r="H10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="8:8">
+      <c r="H11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="8:8">
+      <c r="H15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" ht="17.55" spans="2:10">
+      <c r="B17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J17">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H5" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J5">
+    <row r="18" spans="8:10">
+      <c r="H18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J18">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H6" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J6">
+    <row r="19" spans="8:10">
+      <c r="H19" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J19">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H7" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="J7">
+    <row r="20" spans="8:10">
+      <c r="H20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H8" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8">
+    <row r="21" spans="8:10">
+      <c r="H21" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J21">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H9" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9">
+    <row r="22" spans="8:10">
+      <c r="H22" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J22">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H10" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="J10">
+    <row r="23" spans="8:10">
+      <c r="H23" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J23">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H11" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="J11">
+    <row r="24" spans="8:10">
+      <c r="H24" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J24">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H12" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J12">
+    <row r="25" spans="8:10">
+      <c r="H25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J25">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H13" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="J13">
+    <row r="26" spans="8:10">
+      <c r="H26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J26">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="J14">
+    <row r="27" spans="8:10">
+      <c r="H27" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J27">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H20" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H25" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
-      </c>
+    <row r="28" spans="8:8">
       <c r="H28" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="8:8">
       <c r="H29" t="s">
-        <v>101</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="8:8">
+      <c r="H30" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="8:8">
+      <c r="H31" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="8:8">
+      <c r="H32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="8:8">
+      <c r="H33" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="8:8">
+      <c r="H34" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="8:8">
+      <c r="H35" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="36" spans="8:8">
+      <c r="H36" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="8:8">
+      <c r="H37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="38" spans="8:8">
+      <c r="H38" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="219" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="17.55" spans="8:10">
+      <c r="H5" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="17.55" spans="8:10">
+      <c r="H6" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="8:10">
+      <c r="H7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -4,16 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920" tabRatio="694" firstSheet="1" activeTab="2"/>
+    <workbookView windowHeight="16760" tabRatio="694" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
     <sheet name="ElementEnum" sheetId="7" r:id="rId2"/>
-    <sheet name="RaceEnum" sheetId="10" r:id="rId3"/>
-    <sheet name="PassiveEnum" sheetId="11" r:id="rId4"/>
-    <sheet name="ItemEnum" sheetId="8" r:id="rId5"/>
-    <sheet name="BuffEnum" sheetId="9" r:id="rId6"/>
-    <sheet name="GroupEnum" sheetId="12" r:id="rId7"/>
+    <sheet name="EntityTypeEnum" sheetId="13" r:id="rId3"/>
+    <sheet name="RaceEnum" sheetId="10" r:id="rId4"/>
+    <sheet name="PassiveEnum" sheetId="11" r:id="rId5"/>
+    <sheet name="ItemEnum" sheetId="8" r:id="rId6"/>
+    <sheet name="BuffEnum" sheetId="9" r:id="rId7"/>
+    <sheet name="GroupEnum" sheetId="12" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="125">
   <si>
     <t>##var</t>
   </si>
@@ -149,6 +150,21 @@
     <t>水</t>
   </si>
   <si>
+    <t>EntityTypeEnum</t>
+  </si>
+  <si>
+    <t>这里是二进制</t>
+  </si>
+  <si>
+    <t>Pokemon</t>
+  </si>
+  <si>
+    <t>Building</t>
+  </si>
+  <si>
+    <t>Terrain</t>
+  </si>
+  <si>
     <t>RaceEnum</t>
   </si>
   <si>
@@ -383,13 +399,16 @@
     <t>GroupEnum</t>
   </si>
   <si>
-    <t>All</t>
-  </si>
-  <si>
     <t>友方</t>
   </si>
   <si>
     <t>敌方</t>
+  </si>
+  <si>
+    <t>敌我双方</t>
+  </si>
+  <si>
+    <t>友方|敌方</t>
   </si>
 </sst>
 </file>
@@ -402,7 +421,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,13 +431,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -576,7 +588,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -759,12 +771,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -778,12 +784,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -824,6 +824,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFDEE0E3"/>
       </left>
@@ -834,21 +849,6 @@
         <color rgb="FFDEE0E3"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFDEE0E3"/>
-      </top>
-      <bottom style="medium">
         <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
@@ -984,137 +984,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1127,22 +1127,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
@@ -1154,13 +1157,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1589,7 +1592,7 @@
       </c>
     </row>
     <row r="5" spans="8:10">
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="16" t="s">
         <v>21</v>
       </c>
       <c r="J5">
@@ -1597,7 +1600,7 @@
       </c>
     </row>
     <row r="6" spans="8:10">
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="16" t="s">
         <v>22</v>
       </c>
       <c r="J6">
@@ -1605,7 +1608,7 @@
       </c>
     </row>
     <row r="7" spans="8:10">
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="16" t="s">
         <v>23</v>
       </c>
       <c r="J7">
@@ -1613,7 +1616,7 @@
       </c>
     </row>
     <row r="8" spans="8:10">
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="16" t="s">
         <v>24</v>
       </c>
       <c r="J8">
@@ -1621,7 +1624,7 @@
       </c>
     </row>
     <row r="9" spans="8:10">
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="16" t="s">
         <v>25</v>
       </c>
       <c r="J9">
@@ -1629,7 +1632,7 @@
       </c>
     </row>
     <row r="10" spans="8:10">
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="16" t="s">
         <v>26</v>
       </c>
       <c r="J10">
@@ -1637,7 +1640,7 @@
       </c>
     </row>
     <row r="11" spans="8:10">
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="16" t="s">
         <v>27</v>
       </c>
       <c r="J11">
@@ -1645,7 +1648,7 @@
       </c>
     </row>
     <row r="12" spans="8:10">
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="16" t="s">
         <v>28</v>
       </c>
       <c r="J12">
@@ -1653,7 +1656,7 @@
       </c>
     </row>
     <row r="13" spans="8:10">
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="16" t="s">
         <v>29</v>
       </c>
       <c r="J13">
@@ -1661,7 +1664,7 @@
       </c>
     </row>
     <row r="14" spans="8:10">
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="16" t="s">
         <v>30</v>
       </c>
       <c r="J14">
@@ -1669,7 +1672,7 @@
       </c>
     </row>
     <row r="15" spans="8:10">
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="16" t="s">
         <v>31</v>
       </c>
       <c r="J15">
@@ -1677,7 +1680,7 @@
       </c>
     </row>
     <row r="16" spans="8:10">
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="16" t="s">
         <v>32</v>
       </c>
       <c r="J16">
@@ -1841,8 +1844,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1930,9 +1933,154 @@
       </c>
       <c r="L3" s="1"/>
     </row>
+    <row r="4" spans="2:11">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="8:10">
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="8:10">
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="8:10">
+      <c r="H7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="219" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
     <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -1946,7 +2094,7 @@
     </row>
     <row r="5" spans="8:10">
       <c r="H5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1954,7 +2102,7 @@
     </row>
     <row r="6" spans="8:10">
       <c r="H6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -1962,7 +2110,7 @@
     </row>
     <row r="7" spans="8:10">
       <c r="H7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J7">
         <v>3</v>
@@ -1970,7 +2118,7 @@
     </row>
     <row r="8" spans="8:10">
       <c r="H8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -1978,7 +2126,7 @@
     </row>
     <row r="9" spans="8:10">
       <c r="H9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1986,7 +2134,7 @@
     </row>
     <row r="10" spans="8:10">
       <c r="H10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -2001,7 +2149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L22"/>
@@ -2098,7 +2246,7 @@
     </row>
     <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -2111,376 +2259,148 @@
       </c>
     </row>
     <row r="5" ht="17.55" spans="8:10">
-      <c r="H5" s="12" t="s">
-        <v>46</v>
+      <c r="H5" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="17.55" spans="8:10">
-      <c r="H6" s="13" t="s">
-        <v>47</v>
+      <c r="H6" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
     <row r="7" ht="17.55" spans="8:10">
-      <c r="H7" s="13" t="s">
-        <v>48</v>
+      <c r="H7" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
     </row>
     <row r="8" ht="17.55" spans="8:10">
-      <c r="H8" s="13" t="s">
-        <v>49</v>
+      <c r="H8" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="17.55" spans="8:10">
-      <c r="H9" s="13" t="s">
-        <v>50</v>
+      <c r="H9" s="14" t="s">
+        <v>55</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
     </row>
     <row r="10" ht="17.55" spans="8:10">
-      <c r="H10" s="13" t="s">
-        <v>51</v>
+      <c r="H10" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="8:10">
-      <c r="H11" s="14" t="s">
-        <v>52</v>
+      <c r="H11" s="15" t="s">
+        <v>57</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="8:10">
-      <c r="H12" s="14" t="s">
-        <v>53</v>
+      <c r="H12" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="8:10">
-      <c r="H13" s="14" t="s">
-        <v>54</v>
+      <c r="H13" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="J13">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="8:10">
-      <c r="H14" s="14" t="s">
-        <v>55</v>
+      <c r="H14" s="15" t="s">
+        <v>60</v>
       </c>
       <c r="J14">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="8:10">
-      <c r="H15" s="14" t="s">
-        <v>56</v>
+      <c r="H15" s="15" t="s">
+        <v>61</v>
       </c>
       <c r="J15">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="8:10">
-      <c r="H16" s="14" t="s">
-        <v>57</v>
+      <c r="H16" s="15" t="s">
+        <v>62</v>
       </c>
       <c r="J16">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="8:10">
-      <c r="H17" s="14" t="s">
-        <v>58</v>
+      <c r="H17" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="J17">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="8:10">
-      <c r="H18" s="14" t="s">
-        <v>59</v>
+      <c r="H18" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="J18">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="8:10">
-      <c r="H19" s="14" t="s">
-        <v>60</v>
+      <c r="H19" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="J19">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="8:10">
-      <c r="H20" s="14" t="s">
-        <v>61</v>
+      <c r="H20" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="J20">
         <v>16</v>
       </c>
     </row>
     <row r="21" spans="8:10">
-      <c r="H21" s="14" t="s">
-        <v>62</v>
+      <c r="H21" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="J21">
         <v>17</v>
       </c>
     </row>
     <row r="22" spans="8:10">
-      <c r="H22" s="14" t="s">
-        <v>63</v>
+      <c r="H22" s="15" t="s">
+        <v>68</v>
       </c>
       <c r="J22">
         <v>18</v>
       </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
-  <cols>
-    <col min="2" max="2" width="15.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="219" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="2:10">
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="8:8">
-      <c r="H5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="8:10">
-      <c r="H9" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-    </row>
-    <row r="14" spans="8:10">
-      <c r="H14" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-    </row>
-    <row r="15" spans="8:10">
-      <c r="H15" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-    </row>
-    <row r="16" spans="8:10">
-      <c r="H16" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-    </row>
-    <row r="17" spans="8:10">
-      <c r="H17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-    </row>
-    <row r="18" spans="8:10">
-      <c r="H18" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-    </row>
-    <row r="19" spans="8:10">
-      <c r="H19" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-    </row>
-    <row r="20" spans="8:10">
-      <c r="H20" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-    </row>
-    <row r="21" spans="8:10">
-      <c r="H21" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-    </row>
-    <row r="22" spans="8:10">
-      <c r="H22" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-    </row>
-    <row r="23" spans="8:10">
-      <c r="H23" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2494,10 +2414,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="13.75" customWidth="1"/>
+    <col min="2" max="2" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2586,216 +2506,129 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>36</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="8:8">
       <c r="H5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="8:10">
+      <c r="H9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="8:10">
+      <c r="H14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="8:10">
+      <c r="H15" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" spans="8:10">
+      <c r="H16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="8:10">
+      <c r="H17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="8:10">
+      <c r="H18" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+    </row>
+    <row r="19" spans="8:10">
+      <c r="H19" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+    </row>
+    <row r="20" spans="8:10">
+      <c r="H20" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+    </row>
+    <row r="21" spans="8:10">
+      <c r="H21" s="10" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="6" spans="8:8">
-      <c r="H6" t="s">
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+    </row>
+    <row r="22" spans="8:10">
+      <c r="H22" s="10" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="7" spans="8:8">
-      <c r="H7" t="s">
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+    </row>
+    <row r="23" spans="8:10">
+      <c r="H23" s="10" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="8:8">
-      <c r="H8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="8:8">
-      <c r="H9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="8:8">
-      <c r="H10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="8:8">
-      <c r="H11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8">
-      <c r="B14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="8:8">
-      <c r="H15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" ht="17.55" spans="2:10">
-      <c r="B17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="8:10">
-      <c r="H18" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="8:10">
-      <c r="H19" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="J19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="8:10">
-      <c r="H20" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="J20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="8:10">
-      <c r="H21" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="J21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="8:10">
-      <c r="H22" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="8:10">
-      <c r="H23" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="J23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="8:10">
-      <c r="H24" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J24">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="8:10">
-      <c r="H25" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="J25">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="8:10">
-      <c r="H26" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J26">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="8:10">
-      <c r="H27" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J27">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="8:8">
-      <c r="H28" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="8:8">
-      <c r="H29" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="8:8">
-      <c r="H30" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="8:8">
-      <c r="H31" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" spans="8:8">
-      <c r="H32" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" spans="8:8">
-      <c r="H33" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="34" spans="8:8">
-      <c r="H34" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="35" spans="8:8">
-      <c r="H35" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="8:8">
-      <c r="H36" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="37" spans="8:8">
-      <c r="H37" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" spans="8:8">
-      <c r="H38" t="s">
-        <v>114</v>
-      </c>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2809,8 +2642,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="2" max="2" width="13.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2898,42 +2734,361 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="8:8">
+      <c r="H5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
+      <c r="H6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="8:8">
+      <c r="H7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="8:8">
+      <c r="H8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="8:8">
+      <c r="H9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="8:8">
+      <c r="H10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="8:8">
+      <c r="H11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="8:8">
+      <c r="H15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" ht="17.55"/>
+    <row r="17" ht="17.55" spans="2:10">
+      <c r="B17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="8:10">
+      <c r="H18" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="8:10">
+      <c r="H19" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="8:10">
+      <c r="H20" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="8:10">
+      <c r="H21" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="8:10">
+      <c r="H22" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="8:10">
+      <c r="H23" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="J23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="8:10">
+      <c r="H24" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="8:10">
+      <c r="H25" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="8:10">
+      <c r="H26" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="8:10">
+      <c r="H27" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="J27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="8:8">
+      <c r="H28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="8:8">
+      <c r="H29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="8:8">
+      <c r="H30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="8:8">
+      <c r="H31" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="8:8">
+      <c r="H32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="8:8">
+      <c r="H33" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="8:8">
+      <c r="H34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="8:8">
+      <c r="H35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="8:8">
+      <c r="H36" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="8:8">
+      <c r="H37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="8:8">
+      <c r="H38" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="219" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" ht="17.55" spans="2:11">
+      <c r="B4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="5" ht="17.55" spans="8:10">
-      <c r="H5" s="4" t="s">
-        <v>116</v>
+      <c r="H5" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="17.55" spans="8:10">
-      <c r="H6" s="5" t="s">
-        <v>117</v>
+    <row r="6" spans="8:10">
+      <c r="H6" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="8:10">
-      <c r="H7" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
+      <c r="H7" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980FDE7A-C5CC-4D7B-9190-26CFB04AF25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="16760" tabRatio="694" firstSheet="1" activeTab="7"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="694" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PokemonEnum" sheetId="6" r:id="rId1"/>
@@ -25,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -330,9 +334,6 @@
     <t>BuffEnum</t>
   </si>
   <si>
-    <t>测试0</t>
-  </si>
-  <si>
     <t>易损</t>
   </si>
   <si>
@@ -409,19 +410,17 @@
   </si>
   <si>
     <t>友方|敌方</t>
+  </si>
+  <si>
+    <t>下次攻击伤害三倍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -433,6 +432,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -440,155 +440,25 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <sz val="9.8000000000000007"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -597,7 +467,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79955442976165"/>
+        <fgColor theme="9" tint="0.79952391125217448"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -609,13 +479,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -625,182 +495,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -866,255 +562,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1124,20 +578,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
@@ -1166,62 +611,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1479,19 +886,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="35.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1513,15 +920,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1547,7 +954,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219.75" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1577,117 +984,117 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="17.55" spans="2:10">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:10">
-      <c r="H5" s="16" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="13" t="s">
         <v>21</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="8:10">
-      <c r="H6" s="16" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H6" s="13" t="s">
         <v>22</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="8:10">
-      <c r="H7" s="16" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" s="13" t="s">
         <v>23</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="8:10">
-      <c r="H8" s="16" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" s="13" t="s">
         <v>24</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="8:10">
-      <c r="H9" s="16" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" s="13" t="s">
         <v>25</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="8:10">
-      <c r="H10" s="16" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H10" s="13" t="s">
         <v>26</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="8:10">
-      <c r="H11" s="16" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" s="13" t="s">
         <v>27</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="8:10">
-      <c r="H12" s="16" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" s="13" t="s">
         <v>28</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="8:10">
-      <c r="H13" s="16" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" s="13" t="s">
         <v>29</v>
       </c>
       <c r="J13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="8:10">
-      <c r="H14" s="16" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="13" t="s">
         <v>30</v>
       </c>
       <c r="J14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="8:10">
-      <c r="H15" s="16" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" s="13" t="s">
         <v>31</v>
       </c>
       <c r="J15">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="8:10">
-      <c r="H16" s="16" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="13" t="s">
         <v>32</v>
       </c>
       <c r="J16">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>33</v>
       </c>
@@ -1701,7 +1108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="8:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H26" t="s">
         <v>34</v>
       </c>
@@ -1713,18 +1120,17 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1746,15 +1152,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1780,7 +1186,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1810,7 +1216,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>35</v>
       </c>
@@ -1824,7 +1230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:10">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H5" t="s">
         <v>37</v>
       </c>
@@ -1836,18 +1242,17 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1869,15 +1274,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1903,7 +1308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1933,7 +1338,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>38</v>
       </c>
@@ -1953,7 +1358,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="8:10">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H5" t="s">
         <v>40</v>
       </c>
@@ -1961,7 +1366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="8:10">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H6" t="s">
         <v>41</v>
       </c>
@@ -1969,7 +1374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="8:10">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H7" t="s">
         <v>42</v>
       </c>
@@ -1981,18 +1386,17 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2014,15 +1418,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2048,7 +1452,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2078,7 +1482,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>43</v>
       </c>
@@ -2092,7 +1496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:10">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H5" t="s">
         <v>44</v>
       </c>
@@ -2100,7 +1504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="8:10">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H6" t="s">
         <v>45</v>
       </c>
@@ -2108,7 +1512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="8:10">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H7" t="s">
         <v>46</v>
       </c>
@@ -2116,7 +1520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="8:10">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H8" t="s">
         <v>47</v>
       </c>
@@ -2124,7 +1528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="8:10">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H9" t="s">
         <v>48</v>
       </c>
@@ -2132,7 +1536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="8:10">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H10" t="s">
         <v>49</v>
       </c>
@@ -2144,21 +1548,20 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2180,15 +1583,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2214,7 +1617,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2244,7 +1647,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>50</v>
       </c>
@@ -2258,144 +1661,144 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="17.55" spans="8:10">
-      <c r="H5" s="13" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="10" t="s">
         <v>51</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="17.55" spans="8:10">
-      <c r="H6" s="14" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H6" s="11" t="s">
         <v>52</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="17.55" spans="8:10">
-      <c r="H7" s="14" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" s="11" t="s">
         <v>53</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="17.55" spans="8:10">
-      <c r="H8" s="14" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" s="11" t="s">
         <v>54</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="17.55" spans="8:10">
-      <c r="H9" s="14" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" s="11" t="s">
         <v>55</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="17.55" spans="8:10">
-      <c r="H10" s="14" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H10" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="8:10">
-      <c r="H11" s="15" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" s="12" t="s">
         <v>57</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="8:10">
-      <c r="H12" s="15" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" s="12" t="s">
         <v>58</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="8:10">
-      <c r="H13" s="15" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" s="12" t="s">
         <v>59</v>
       </c>
       <c r="J13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="8:10">
-      <c r="H14" s="15" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="8:10">
-      <c r="H15" s="15" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" s="12" t="s">
         <v>61</v>
       </c>
       <c r="J15">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="8:10">
-      <c r="H16" s="15" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="12" t="s">
         <v>62</v>
       </c>
       <c r="J16">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="8:10">
-      <c r="H17" s="15" t="s">
+    <row r="17" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H17" s="12" t="s">
         <v>63</v>
       </c>
       <c r="J17">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="8:10">
-      <c r="H18" s="15" t="s">
+    <row r="18" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H18" s="12" t="s">
         <v>64</v>
       </c>
       <c r="J18">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="8:10">
-      <c r="H19" s="15" t="s">
+    <row r="19" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H19" s="12" t="s">
         <v>65</v>
       </c>
       <c r="J19">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="8:10">
-      <c r="H20" s="15" t="s">
+    <row r="20" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H20" s="12" t="s">
         <v>66</v>
       </c>
       <c r="J20">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="8:10">
-      <c r="H21" s="15" t="s">
+    <row r="21" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H21" s="12" t="s">
         <v>67</v>
       </c>
       <c r="J21">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="8:10">
-      <c r="H22" s="15" t="s">
+    <row r="22" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H22" s="12" t="s">
         <v>68</v>
       </c>
       <c r="J22">
@@ -2406,21 +1809,20 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2442,15 +1844,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2476,7 +1878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2506,7 +1908,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>69</v>
       </c>
@@ -2520,26 +1922,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
-      <c r="B8" s="7" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" t="s">
         <v>72</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="8:10">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H9" t="s">
         <v>73</v>
       </c>
@@ -2547,108 +1949,107 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>74</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" spans="8:10">
-      <c r="H14" s="9" t="s">
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-    </row>
-    <row r="15" spans="8:10">
-      <c r="H15" s="9" t="s">
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-    </row>
-    <row r="16" spans="8:10">
-      <c r="H16" s="9" t="s">
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" spans="8:10">
-      <c r="H17" s="9" t="s">
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H17" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" spans="8:10">
-      <c r="H18" s="9" t="s">
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H18" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-    </row>
-    <row r="19" spans="8:10">
-      <c r="H19" s="10" t="s">
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H19" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-    </row>
-    <row r="20" spans="8:10">
-      <c r="H20" s="10" t="s">
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H20" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-    </row>
-    <row r="21" spans="8:10">
-      <c r="H21" s="10" t="s">
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H21" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-    </row>
-    <row r="22" spans="8:10">
-      <c r="H22" s="10" t="s">
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H22" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-    </row>
-    <row r="23" spans="8:10">
-      <c r="H23" s="10" t="s">
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H23" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L38"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:L42"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2670,15 +2071,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2704,7 +2105,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2734,7 +2135,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>85</v>
       </c>
@@ -2745,42 +2146,42 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="8:8">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="8:8">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H9" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="8:8">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H10" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="8:8">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>94</v>
       </c>
@@ -2791,177 +2192,175 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="8:8">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H15" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="16" ht="17.55"/>
-    <row r="17" ht="17.55" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>97</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>98</v>
+      <c r="H17" s="15" t="s">
+        <v>124</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="8:10">
-      <c r="H18" s="6" t="s">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H19" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="8:10">
-      <c r="H19" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="J19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="8:10">
-      <c r="H20" s="6" t="s">
-        <v>101</v>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H20" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="J20">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="8:10">
-      <c r="H21" s="6" t="s">
-        <v>102</v>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H21" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="J21">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="8:10">
-      <c r="H22" s="6" t="s">
-        <v>103</v>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H22" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="J22">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="8:10">
-      <c r="H23" s="6" t="s">
-        <v>104</v>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H23" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="J23">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="8:10">
-      <c r="H24" s="6" t="s">
-        <v>105</v>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H24" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="8:10">
-      <c r="H25" s="6" t="s">
-        <v>106</v>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H25" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="J25">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="8:10">
-      <c r="H26" s="6" t="s">
-        <v>107</v>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H26" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="J26">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="8:10">
-      <c r="H27" s="6" t="s">
-        <v>108</v>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H27" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="J27">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="8:8">
-      <c r="H28" t="s">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="8:8">
-      <c r="H29" t="s">
+    <row r="34" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H34" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="8:8">
-      <c r="H30" t="s">
+    <row r="35" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H35" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="8:8">
-      <c r="H31" t="s">
+    <row r="36" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="8:8">
-      <c r="H32" t="s">
+    <row r="37" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H37" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="33" spans="8:8">
-      <c r="H33" t="s">
+    <row r="38" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H38" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="8:8">
-      <c r="H34" t="s">
+    <row r="39" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="8:8">
-      <c r="H35" t="s">
+    <row r="40" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H40" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="8:8">
-      <c r="H36" t="s">
+    <row r="41" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H41" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="37" spans="8:8">
-      <c r="H37" t="s">
+    <row r="42" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="38" spans="8:8">
-      <c r="H38" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2983,15 +2382,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3017,7 +2416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3047,9 +2446,9 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="17.55" spans="2:11">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -3057,7 +2456,7 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" t="s">
         <v>36</v>
       </c>
       <c r="J4">
@@ -3067,35 +2466,35 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" ht="17.55" spans="8:10">
-      <c r="H5" s="5" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H6" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="8:10">
-      <c r="H6" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="8:10">
-      <c r="H7" s="6" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="J7" t="s">
         <v>123</v>
-      </c>
-      <c r="J7" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/Datas/__enums__.xlsx
+++ b/Excel/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980FDE7A-C5CC-4D7B-9190-26CFB04AF25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA7C120-F8EF-4250-993D-DD1865A9AE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="694" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <sheet name="PassiveEnum" sheetId="11" r:id="rId5"/>
     <sheet name="ItemEnum" sheetId="8" r:id="rId6"/>
     <sheet name="BuffEnum" sheetId="9" r:id="rId7"/>
-    <sheet name="GroupEnum" sheetId="12" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="97">
   <si>
     <t>##var</t>
   </si>
@@ -295,42 +294,6 @@
     <t>脏拖把</t>
   </si>
   <si>
-    <t>BuffTargetTypeEnum</t>
-  </si>
-  <si>
-    <t>我方单体</t>
-  </si>
-  <si>
-    <t>我方全体</t>
-  </si>
-  <si>
-    <t>敌方单体</t>
-  </si>
-  <si>
-    <t>敌方全体</t>
-  </si>
-  <si>
-    <t>我方部分</t>
-  </si>
-  <si>
-    <t>敌人部分</t>
-  </si>
-  <si>
-    <t>敌我全体</t>
-  </si>
-  <si>
-    <t>敌我部分</t>
-  </si>
-  <si>
-    <t>BuffType</t>
-  </si>
-  <si>
-    <t>永久</t>
-  </si>
-  <si>
-    <t>倒计时</t>
-  </si>
-  <si>
     <t>BuffEnum</t>
   </si>
   <si>
@@ -362,54 +325,6 @@
   </si>
   <si>
     <t>高额伤害</t>
-  </si>
-  <si>
-    <t>永久速度</t>
-  </si>
-  <si>
-    <t>永久固定防御力</t>
-  </si>
-  <si>
-    <t>永久固定力量</t>
-  </si>
-  <si>
-    <t>永久固定生命值</t>
-  </si>
-  <si>
-    <t>临时固定速度</t>
-  </si>
-  <si>
-    <t>临时固定力量</t>
-  </si>
-  <si>
-    <t>临时固定防御</t>
-  </si>
-  <si>
-    <t>恢复百分比生命</t>
-  </si>
-  <si>
-    <t>受到固定真实伤害</t>
-  </si>
-  <si>
-    <t>下次攻击伤害倍率</t>
-  </si>
-  <si>
-    <t>降低百分比力量</t>
-  </si>
-  <si>
-    <t>GroupEnum</t>
-  </si>
-  <si>
-    <t>友方</t>
-  </si>
-  <si>
-    <t>敌方</t>
-  </si>
-  <si>
-    <t>敌我双方</t>
-  </si>
-  <si>
-    <t>友方|敌方</t>
   </si>
   <si>
     <t>下次攻击伤害三倍</t>
@@ -611,11 +526,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -920,13 +835,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1152,13 +1067,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1274,13 +1189,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1418,13 +1333,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1583,13 +1498,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1844,13 +1759,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -2043,7 +1958,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.75" customWidth="1"/>
@@ -2071,13 +1986,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -2142,333 +2057,16 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="4" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H18" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H19" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="J19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H20" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H21" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="J21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H22" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H23" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H24" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="J24">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H25" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J25">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H26" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="J26">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H27" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="J27">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H32" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H33" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H34" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="35" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H35" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H36" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="37" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H37" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H38" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="39" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H39" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="40" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H41" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="42" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H42" t="s">
-        <v>118</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="171" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H5" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -2476,7 +2074,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H6" s="4" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -2484,10 +2082,66 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H7" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="J7" t="s">
-        <v>123</v>
+        <v>88</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J14">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
